--- a/templates/_masters/FIN-004-dscr-tracker-BLANK.xlsx
+++ b/templates/_masters/FIN-004-dscr-tracker-BLANK.xlsx
@@ -317,16 +317,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00CCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00CCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00CCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00CCCCCC"/>
       </bottom>
     </border>
   </borders>
